--- a/GACPAQ pages.xlsx
+++ b/GACPAQ pages.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/doncastillo/Code/gacpaq/gacpaq-app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56686A86-3F82-794B-9BE7-36B735D17A6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E76F6DB1-ED31-AF4B-BE57-88CA974F4891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20060" yWindow="-20860" windowWidth="38400" windowHeight="21100" activeTab="5" xr2:uid="{F0D6E043-EC2B-F746-8C39-25C7730C9E54}"/>
+    <workbookView xWindow="19720" yWindow="-21100" windowWidth="38400" windowHeight="21100" activeTab="5" xr2:uid="{F0D6E043-EC2B-F746-8C39-25C7730C9E54}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="969" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="970" uniqueCount="422">
   <si>
     <t>Page Number</t>
   </si>
@@ -8007,7 +8007,9 @@
       <c r="F5" s="53" t="s">
         <v>337</v>
       </c>
-      <c r="G5" s="55"/>
+      <c r="G5" s="56" t="s">
+        <v>415</v>
+      </c>
       <c r="H5" s="53" t="s">
         <v>337</v>
       </c>

--- a/GACPAQ pages.xlsx
+++ b/GACPAQ pages.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/doncastillo/Code/gacpaq/gacpaq-app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E76F6DB1-ED31-AF4B-BE57-88CA974F4891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC74EE7C-8643-E448-9E10-69FBF77E6FEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19720" yWindow="-21100" windowWidth="38400" windowHeight="21100" activeTab="5" xr2:uid="{F0D6E043-EC2B-F746-8C39-25C7730C9E54}"/>
+    <workbookView xWindow="18060" yWindow="-20240" windowWidth="38400" windowHeight="21100" activeTab="5" xr2:uid="{F0D6E043-EC2B-F746-8C39-25C7730C9E54}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="970" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="973" uniqueCount="423">
   <si>
     <t>Page Number</t>
   </si>
@@ -2881,6 +2881,9 @@
   </si>
   <si>
     <t>on-going (12)</t>
+  </si>
+  <si>
+    <t>on-going (13)</t>
   </si>
 </sst>
 </file>
@@ -8249,7 +8252,9 @@
       <c r="J9" s="56" t="s">
         <v>419</v>
       </c>
-      <c r="K9" s="55"/>
+      <c r="K9" s="54" t="s">
+        <v>422</v>
+      </c>
       <c r="L9" s="40" t="s">
         <v>416</v>
       </c>
@@ -8305,7 +8310,9 @@
       <c r="J10" s="56" t="s">
         <v>419</v>
       </c>
-      <c r="K10" s="55"/>
+      <c r="K10" s="54" t="s">
+        <v>422</v>
+      </c>
       <c r="L10" s="40" t="s">
         <v>281</v>
       </c>
@@ -8361,7 +8368,9 @@
       <c r="J11" s="56" t="s">
         <v>419</v>
       </c>
-      <c r="K11" s="55"/>
+      <c r="K11" s="54" t="s">
+        <v>422</v>
+      </c>
       <c r="L11" s="40" t="s">
         <v>283</v>
       </c>

--- a/GACPAQ pages.xlsx
+++ b/GACPAQ pages.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/doncastillo/Code/gacpaq/gacpaq-app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC74EE7C-8643-E448-9E10-69FBF77E6FEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75C33FF3-592B-564B-A718-8AD9A7614087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18060" yWindow="-20240" windowWidth="38400" windowHeight="21100" activeTab="5" xr2:uid="{F0D6E043-EC2B-F746-8C39-25C7730C9E54}"/>
+    <workbookView xWindow="18260" yWindow="-21100" windowWidth="38400" windowHeight="21100" activeTab="5" xr2:uid="{F0D6E043-EC2B-F746-8C39-25C7730C9E54}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/GACPAQ pages.xlsx
+++ b/GACPAQ pages.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/doncastillo/Code/gacpaq/gacpaq-app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC74EE7C-8643-E448-9E10-69FBF77E6FEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10B78506-DD8D-A14D-901A-1884CBCBA742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18060" yWindow="-20240" windowWidth="38400" windowHeight="21100" activeTab="5" xr2:uid="{F0D6E043-EC2B-F746-8C39-25C7730C9E54}"/>
+    <workbookView xWindow="-20140" yWindow="-21100" windowWidth="19200" windowHeight="19620" activeTab="5" xr2:uid="{F0D6E043-EC2B-F746-8C39-25C7730C9E54}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="973" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="423">
   <si>
     <t>Page Number</t>
   </si>
@@ -3312,7 +3312,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3503,6 +3503,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -8249,8 +8252,8 @@
       <c r="I9" s="53" t="s">
         <v>337</v>
       </c>
-      <c r="J9" s="56" t="s">
-        <v>419</v>
+      <c r="J9" s="53" t="s">
+        <v>343</v>
       </c>
       <c r="K9" s="54" t="s">
         <v>422</v>
@@ -8298,8 +8301,8 @@
       <c r="F10" s="53" t="s">
         <v>337</v>
       </c>
-      <c r="G10" s="53" t="s">
-        <v>337</v>
+      <c r="G10" s="56" t="s">
+        <v>415</v>
       </c>
       <c r="H10" s="53" t="s">
         <v>337</v>
@@ -8310,9 +8313,7 @@
       <c r="J10" s="56" t="s">
         <v>419</v>
       </c>
-      <c r="K10" s="54" t="s">
-        <v>422</v>
-      </c>
+      <c r="K10" s="80"/>
       <c r="L10" s="40" t="s">
         <v>281</v>
       </c>
@@ -8353,11 +8354,11 @@
       <c r="E11" s="53" t="s">
         <v>337</v>
       </c>
-      <c r="F11" s="57" t="s">
-        <v>344</v>
-      </c>
-      <c r="G11" s="56" t="s">
-        <v>415</v>
+      <c r="F11" s="53" t="s">
+        <v>337</v>
+      </c>
+      <c r="G11" s="53" t="s">
+        <v>337</v>
       </c>
       <c r="H11" s="53" t="s">
         <v>337</v>
@@ -8365,8 +8366,8 @@
       <c r="I11" s="53" t="s">
         <v>337</v>
       </c>
-      <c r="J11" s="56" t="s">
-        <v>419</v>
+      <c r="J11" s="53" t="s">
+        <v>343</v>
       </c>
       <c r="K11" s="54" t="s">
         <v>422</v>

--- a/GACPAQ pages.xlsx
+++ b/GACPAQ pages.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/doncastillo/Code/gacpaq/gacpaq-app/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/doncastillo/Code/gacpaq/gac-paq-app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10B78506-DD8D-A14D-901A-1884CBCBA742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DB6051E-5E4E-194A-A574-BADF491ACEBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20140" yWindow="-21100" windowWidth="19200" windowHeight="19620" activeTab="5" xr2:uid="{F0D6E043-EC2B-F746-8C39-25C7730C9E54}"/>
+    <workbookView xWindow="18260" yWindow="-21000" windowWidth="38400" windowHeight="21000" activeTab="5" xr2:uid="{F0D6E043-EC2B-F746-8C39-25C7730C9E54}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="974" uniqueCount="423">
   <si>
     <t>Page Number</t>
   </si>
@@ -2861,9 +2861,6 @@
     <t>Respostas enviadas</t>
   </si>
   <si>
-    <t>on-going</t>
-  </si>
-  <si>
     <t>India - English</t>
   </si>
   <si>
@@ -2884,6 +2881,9 @@
   </si>
   <si>
     <t>on-going (13)</t>
+  </si>
+  <si>
+    <t>on-going (14)</t>
   </si>
 </sst>
 </file>
@@ -3312,7 +3312,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3503,9 +3503,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5345,7 +5342,7 @@
       </c>
       <c r="E40" s="31"/>
       <c r="F40" s="32" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="G40" s="32"/>
       <c r="H40" s="31" t="s">
@@ -8013,8 +8010,8 @@
       <c r="F5" s="53" t="s">
         <v>337</v>
       </c>
-      <c r="G5" s="56" t="s">
-        <v>415</v>
+      <c r="G5" s="53" t="s">
+        <v>337</v>
       </c>
       <c r="H5" s="53" t="s">
         <v>337</v>
@@ -8022,10 +8019,12 @@
       <c r="I5" s="53" t="s">
         <v>337</v>
       </c>
-      <c r="J5" s="56" t="s">
-        <v>419</v>
-      </c>
-      <c r="K5" s="55"/>
+      <c r="J5" s="53" t="s">
+        <v>337</v>
+      </c>
+      <c r="K5" s="54" t="s">
+        <v>422</v>
+      </c>
       <c r="L5" s="40" t="s">
         <v>335</v>
       </c>
@@ -8198,7 +8197,7 @@
         <v>343</v>
       </c>
       <c r="K8" s="54" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="L8" s="40" t="s">
         <v>336</v>
@@ -8226,10 +8225,10 @@
     </row>
     <row r="9" spans="1:36" ht="27" customHeight="1">
       <c r="A9" s="40" t="s">
+        <v>415</v>
+      </c>
+      <c r="B9" s="41" t="s">
         <v>416</v>
-      </c>
-      <c r="B9" s="41" t="s">
-        <v>417</v>
       </c>
       <c r="C9" s="53" t="s">
         <v>337</v>
@@ -8256,10 +8255,10 @@
         <v>343</v>
       </c>
       <c r="K9" s="54" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="L9" s="40" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="M9" s="48"/>
       <c r="N9" s="48"/>
@@ -8301,8 +8300,8 @@
       <c r="F10" s="53" t="s">
         <v>337</v>
       </c>
-      <c r="G10" s="56" t="s">
-        <v>415</v>
+      <c r="G10" s="53" t="s">
+        <v>337</v>
       </c>
       <c r="H10" s="53" t="s">
         <v>337</v>
@@ -8310,10 +8309,12 @@
       <c r="I10" s="53" t="s">
         <v>337</v>
       </c>
-      <c r="J10" s="56" t="s">
-        <v>419</v>
-      </c>
-      <c r="K10" s="80"/>
+      <c r="J10" s="53" t="s">
+        <v>337</v>
+      </c>
+      <c r="K10" s="54" t="s">
+        <v>422</v>
+      </c>
       <c r="L10" s="40" t="s">
         <v>281</v>
       </c>
@@ -8370,7 +8371,7 @@
         <v>343</v>
       </c>
       <c r="K11" s="54" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="L11" s="40" t="s">
         <v>283</v>
@@ -8428,7 +8429,7 @@
         <v>343</v>
       </c>
       <c r="K12" s="54" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="L12" s="40" t="s">
         <v>285</v>
@@ -8486,7 +8487,7 @@
         <v>343</v>
       </c>
       <c r="K13" s="54" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="L13" s="40" t="s">
         <v>287</v>
@@ -8655,7 +8656,7 @@
         <v>337</v>
       </c>
       <c r="J16" s="56" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="K16" s="55"/>
       <c r="L16" s="40" t="s">
@@ -8709,7 +8710,7 @@
         <v>337</v>
       </c>
       <c r="J17" s="56" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="K17" s="55"/>
       <c r="L17" s="40" t="s">

--- a/GACPAQ pages.xlsx
+++ b/GACPAQ pages.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/doncastillo/Code/gacpaq/gac-paq-app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DB6051E-5E4E-194A-A574-BADF491ACEBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24EFBEE6-6C61-474D-B5F8-3918F106A171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18260" yWindow="-21000" windowWidth="38400" windowHeight="21000" activeTab="5" xr2:uid="{F0D6E043-EC2B-F746-8C39-25C7730C9E54}"/>
+    <workbookView xWindow="-20140" yWindow="-21000" windowWidth="38400" windowHeight="21000" activeTab="5" xr2:uid="{F0D6E043-EC2B-F746-8C39-25C7730C9E54}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="974" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="977" uniqueCount="425">
   <si>
     <t>Page Number</t>
   </si>
@@ -2884,6 +2884,12 @@
   </si>
   <si>
     <t>on-going (14)</t>
+  </si>
+  <si>
+    <t>Ghana - English</t>
+  </si>
+  <si>
+    <t>en-GH</t>
   </si>
 </sst>
 </file>
@@ -3312,7 +3318,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3503,6 +3509,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -7728,7 +7737,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BEEE373-47BE-6F4C-8F66-ACD6798C647F}">
-  <dimension ref="A1:AJ23"/>
+  <dimension ref="A1:AJ24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="17.5" customWidth="1"/>
@@ -8225,40 +8234,22 @@
     </row>
     <row r="9" spans="1:36" ht="27" customHeight="1">
       <c r="A9" s="40" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="B9" s="41" t="s">
-        <v>416</v>
-      </c>
-      <c r="C9" s="53" t="s">
-        <v>337</v>
-      </c>
-      <c r="D9" s="53" t="s">
-        <v>337</v>
-      </c>
-      <c r="E9" s="53" t="s">
-        <v>337</v>
-      </c>
-      <c r="F9" s="53" t="s">
-        <v>337</v>
-      </c>
-      <c r="G9" s="53" t="s">
-        <v>337</v>
-      </c>
-      <c r="H9" s="53" t="s">
-        <v>337</v>
-      </c>
-      <c r="I9" s="53" t="s">
-        <v>337</v>
-      </c>
-      <c r="J9" s="53" t="s">
-        <v>343</v>
-      </c>
-      <c r="K9" s="54" t="s">
-        <v>421</v>
-      </c>
+        <v>424</v>
+      </c>
+      <c r="C9" s="80"/>
+      <c r="D9" s="80"/>
+      <c r="E9" s="80"/>
+      <c r="F9" s="80"/>
+      <c r="G9" s="80"/>
+      <c r="H9" s="80"/>
+      <c r="I9" s="80"/>
+      <c r="J9" s="80"/>
+      <c r="K9" s="80"/>
       <c r="L9" s="40" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="M9" s="48"/>
       <c r="N9" s="48"/>
@@ -8283,10 +8274,10 @@
     </row>
     <row r="10" spans="1:36" ht="27" customHeight="1">
       <c r="A10" s="40" t="s">
-        <v>281</v>
+        <v>415</v>
       </c>
       <c r="B10" s="41" t="s">
-        <v>282</v>
+        <v>416</v>
       </c>
       <c r="C10" s="53" t="s">
         <v>337</v>
@@ -8310,13 +8301,13 @@
         <v>337</v>
       </c>
       <c r="J10" s="53" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="K10" s="54" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="L10" s="40" t="s">
-        <v>281</v>
+        <v>415</v>
       </c>
       <c r="M10" s="48"/>
       <c r="N10" s="48"/>
@@ -8341,10 +8332,10 @@
     </row>
     <row r="11" spans="1:36" ht="27" customHeight="1">
       <c r="A11" s="40" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B11" s="41" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C11" s="53" t="s">
         <v>337</v>
@@ -8368,13 +8359,13 @@
         <v>337</v>
       </c>
       <c r="J11" s="53" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="K11" s="54" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="L11" s="40" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="M11" s="48"/>
       <c r="N11" s="48"/>
@@ -8399,10 +8390,10 @@
     </row>
     <row r="12" spans="1:36" ht="27" customHeight="1">
       <c r="A12" s="40" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B12" s="41" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C12" s="53" t="s">
         <v>337</v>
@@ -8429,10 +8420,10 @@
         <v>343</v>
       </c>
       <c r="K12" s="54" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="L12" s="40" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="M12" s="48"/>
       <c r="N12" s="48"/>
@@ -8457,10 +8448,10 @@
     </row>
     <row r="13" spans="1:36" ht="27" customHeight="1">
       <c r="A13" s="40" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B13" s="41" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C13" s="53" t="s">
         <v>337</v>
@@ -8490,7 +8481,7 @@
         <v>419</v>
       </c>
       <c r="L13" s="40" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="M13" s="48"/>
       <c r="N13" s="48"/>
@@ -8515,10 +8506,10 @@
     </row>
     <row r="14" spans="1:36" ht="27" customHeight="1">
       <c r="A14" s="40" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B14" s="41" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C14" s="53" t="s">
         <v>337</v>
@@ -8544,11 +8535,11 @@
       <c r="J14" s="53" t="s">
         <v>343</v>
       </c>
-      <c r="K14" s="56" t="s">
-        <v>387</v>
+      <c r="K14" s="54" t="s">
+        <v>419</v>
       </c>
       <c r="L14" s="40" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="M14" s="48"/>
       <c r="N14" s="48"/>
@@ -8573,10 +8564,10 @@
     </row>
     <row r="15" spans="1:36" ht="27" customHeight="1">
       <c r="A15" s="40" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B15" s="41" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C15" s="53" t="s">
         <v>337</v>
@@ -8603,10 +8594,10 @@
         <v>343</v>
       </c>
       <c r="K15" s="56" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="L15" s="40" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="M15" s="48"/>
       <c r="N15" s="48"/>
@@ -8631,10 +8622,10 @@
     </row>
     <row r="16" spans="1:36" ht="27" customHeight="1">
       <c r="A16" s="40" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B16" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C16" s="53" t="s">
         <v>337</v>
@@ -8645,22 +8636,26 @@
       <c r="E16" s="53" t="s">
         <v>337</v>
       </c>
-      <c r="F16" s="57" t="s">
-        <v>344</v>
-      </c>
-      <c r="G16" s="55"/>
+      <c r="F16" s="53" t="s">
+        <v>337</v>
+      </c>
+      <c r="G16" s="53" t="s">
+        <v>337</v>
+      </c>
       <c r="H16" s="53" t="s">
         <v>337</v>
       </c>
       <c r="I16" s="53" t="s">
         <v>337</v>
       </c>
-      <c r="J16" s="56" t="s">
-        <v>418</v>
-      </c>
-      <c r="K16" s="55"/>
+      <c r="J16" s="53" t="s">
+        <v>343</v>
+      </c>
+      <c r="K16" s="56" t="s">
+        <v>391</v>
+      </c>
       <c r="L16" s="40" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="M16" s="48"/>
       <c r="N16" s="48"/>
@@ -8683,12 +8678,12 @@
       <c r="AE16" s="48"/>
       <c r="AF16" s="48"/>
     </row>
-    <row r="17" spans="1:32" ht="26">
+    <row r="17" spans="1:32" ht="27" customHeight="1">
       <c r="A17" s="40" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B17" s="41" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C17" s="53" t="s">
         <v>337</v>
@@ -8696,8 +8691,8 @@
       <c r="D17" s="53" t="s">
         <v>337</v>
       </c>
-      <c r="E17" s="57" t="s">
-        <v>345</v>
+      <c r="E17" s="53" t="s">
+        <v>337</v>
       </c>
       <c r="F17" s="57" t="s">
         <v>344</v>
@@ -8714,7 +8709,7 @@
       </c>
       <c r="K17" s="55"/>
       <c r="L17" s="40" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="M17" s="48"/>
       <c r="N17" s="48"/>
@@ -8737,12 +8732,12 @@
       <c r="AE17" s="48"/>
       <c r="AF17" s="48"/>
     </row>
-    <row r="18" spans="1:32" ht="31" customHeight="1">
+    <row r="18" spans="1:32" ht="26">
       <c r="A18" s="40" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B18" s="41" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C18" s="53" t="s">
         <v>337</v>
@@ -8750,29 +8745,25 @@
       <c r="D18" s="53" t="s">
         <v>337</v>
       </c>
-      <c r="E18" s="53" t="s">
-        <v>337</v>
-      </c>
-      <c r="F18" s="53" t="s">
-        <v>337</v>
-      </c>
-      <c r="G18" s="53" t="s">
-        <v>337</v>
-      </c>
+      <c r="E18" s="57" t="s">
+        <v>345</v>
+      </c>
+      <c r="F18" s="57" t="s">
+        <v>344</v>
+      </c>
+      <c r="G18" s="55"/>
       <c r="H18" s="53" t="s">
         <v>337</v>
       </c>
       <c r="I18" s="53" t="s">
         <v>337</v>
       </c>
-      <c r="J18" s="53" t="s">
-        <v>343</v>
-      </c>
-      <c r="K18" s="56" t="s">
-        <v>391</v>
-      </c>
+      <c r="J18" s="56" t="s">
+        <v>418</v>
+      </c>
+      <c r="K18" s="55"/>
       <c r="L18" s="40" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="M18" s="48"/>
       <c r="N18" s="48"/>
@@ -8795,12 +8786,12 @@
       <c r="AE18" s="48"/>
       <c r="AF18" s="48"/>
     </row>
-    <row r="19" spans="1:32" ht="27" customHeight="1">
+    <row r="19" spans="1:32" ht="31" customHeight="1">
       <c r="A19" s="40" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B19" s="41" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C19" s="53" t="s">
         <v>337</v>
@@ -8826,11 +8817,11 @@
       <c r="J19" s="53" t="s">
         <v>343</v>
       </c>
-      <c r="K19" s="54" t="s">
-        <v>388</v>
+      <c r="K19" s="56" t="s">
+        <v>391</v>
       </c>
       <c r="L19" s="40" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="M19" s="48"/>
       <c r="N19" s="48"/>
@@ -8855,10 +8846,10 @@
     </row>
     <row r="20" spans="1:32" ht="27" customHeight="1">
       <c r="A20" s="40" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B20" s="41" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C20" s="53" t="s">
         <v>337</v>
@@ -8884,11 +8875,11 @@
       <c r="J20" s="53" t="s">
         <v>343</v>
       </c>
-      <c r="K20" s="56" t="s">
-        <v>386</v>
+      <c r="K20" s="54" t="s">
+        <v>388</v>
       </c>
       <c r="L20" s="40" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="M20" s="48"/>
       <c r="N20" s="48"/>
@@ -8913,10 +8904,10 @@
     </row>
     <row r="21" spans="1:32" ht="27" customHeight="1">
       <c r="A21" s="40" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B21" s="41" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C21" s="53" t="s">
         <v>337</v>
@@ -8943,10 +8934,10 @@
         <v>343</v>
       </c>
       <c r="K21" s="56" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="L21" s="40" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="M21" s="48"/>
       <c r="N21" s="48"/>
@@ -8971,10 +8962,10 @@
     </row>
     <row r="22" spans="1:32" ht="27" customHeight="1">
       <c r="A22" s="40" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B22" s="41" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C22" s="53" t="s">
         <v>337</v>
@@ -9001,10 +8992,10 @@
         <v>343</v>
       </c>
       <c r="K22" s="56" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="L22" s="40" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="M22" s="48"/>
       <c r="N22" s="48"/>
@@ -9029,10 +9020,10 @@
     </row>
     <row r="23" spans="1:32" ht="27" customHeight="1">
       <c r="A23" s="40" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B23" s="41" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C23" s="53" t="s">
         <v>337</v>
@@ -9062,7 +9053,7 @@
         <v>394</v>
       </c>
       <c r="L23" s="40" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="M23" s="48"/>
       <c r="N23" s="48"/>
@@ -9084,6 +9075,64 @@
       <c r="AD23" s="48"/>
       <c r="AE23" s="48"/>
       <c r="AF23" s="48"/>
+    </row>
+    <row r="24" spans="1:32" ht="27" customHeight="1">
+      <c r="A24" s="40" t="s">
+        <v>307</v>
+      </c>
+      <c r="B24" s="41" t="s">
+        <v>308</v>
+      </c>
+      <c r="C24" s="53" t="s">
+        <v>337</v>
+      </c>
+      <c r="D24" s="53" t="s">
+        <v>337</v>
+      </c>
+      <c r="E24" s="53" t="s">
+        <v>337</v>
+      </c>
+      <c r="F24" s="53" t="s">
+        <v>337</v>
+      </c>
+      <c r="G24" s="53" t="s">
+        <v>337</v>
+      </c>
+      <c r="H24" s="53" t="s">
+        <v>337</v>
+      </c>
+      <c r="I24" s="53" t="s">
+        <v>337</v>
+      </c>
+      <c r="J24" s="53" t="s">
+        <v>343</v>
+      </c>
+      <c r="K24" s="56" t="s">
+        <v>394</v>
+      </c>
+      <c r="L24" s="40" t="s">
+        <v>307</v>
+      </c>
+      <c r="M24" s="48"/>
+      <c r="N24" s="48"/>
+      <c r="O24" s="48"/>
+      <c r="P24" s="48"/>
+      <c r="Q24" s="48"/>
+      <c r="R24" s="48"/>
+      <c r="S24" s="48"/>
+      <c r="T24" s="48"/>
+      <c r="U24" s="48"/>
+      <c r="V24" s="48"/>
+      <c r="W24" s="48"/>
+      <c r="X24" s="48"/>
+      <c r="Y24" s="48"/>
+      <c r="Z24" s="48"/>
+      <c r="AA24" s="48"/>
+      <c r="AB24" s="48"/>
+      <c r="AC24" s="48"/>
+      <c r="AD24" s="48"/>
+      <c r="AE24" s="48"/>
+      <c r="AF24" s="48"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/GACPAQ pages.xlsx
+++ b/GACPAQ pages.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/doncastillo/Code/gacpaq/gac-paq-app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24EFBEE6-6C61-474D-B5F8-3918F106A171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{918DD141-9400-2547-9906-1BF85C017213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20140" yWindow="-21000" windowWidth="38400" windowHeight="21000" activeTab="5" xr2:uid="{F0D6E043-EC2B-F746-8C39-25C7730C9E54}"/>
+    <workbookView xWindow="18260" yWindow="-21000" windowWidth="38400" windowHeight="19220" activeTab="5" xr2:uid="{F0D6E043-EC2B-F746-8C39-25C7730C9E54}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="977" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="981" uniqueCount="425">
   <si>
     <t>Page Number</t>
   </si>
@@ -8239,10 +8239,18 @@
       <c r="B9" s="41" t="s">
         <v>424</v>
       </c>
-      <c r="C9" s="80"/>
-      <c r="D9" s="80"/>
-      <c r="E9" s="80"/>
-      <c r="F9" s="80"/>
+      <c r="C9" s="53" t="s">
+        <v>337</v>
+      </c>
+      <c r="D9" s="53" t="s">
+        <v>337</v>
+      </c>
+      <c r="E9" s="53" t="s">
+        <v>337</v>
+      </c>
+      <c r="F9" s="53" t="s">
+        <v>337</v>
+      </c>
       <c r="G9" s="80"/>
       <c r="H9" s="80"/>
       <c r="I9" s="80"/>

--- a/GACPAQ pages.xlsx
+++ b/GACPAQ pages.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/doncastillo/Code/gacpaq/gac-paq-app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{918DD141-9400-2547-9906-1BF85C017213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE4CA96A-15E5-A241-90A2-BD5CC1540E93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18260" yWindow="-21000" windowWidth="38400" windowHeight="19220" activeTab="5" xr2:uid="{F0D6E043-EC2B-F746-8C39-25C7730C9E54}"/>
+    <workbookView xWindow="2720" yWindow="780" windowWidth="38400" windowHeight="19140" activeTab="5" xr2:uid="{F0D6E043-EC2B-F746-8C39-25C7730C9E54}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -3318,7 +3318,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3509,9 +3509,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -8251,11 +8248,11 @@
       <c r="F9" s="53" t="s">
         <v>337</v>
       </c>
-      <c r="G9" s="80"/>
-      <c r="H9" s="80"/>
-      <c r="I9" s="80"/>
-      <c r="J9" s="80"/>
-      <c r="K9" s="80"/>
+      <c r="G9" s="55"/>
+      <c r="H9" s="55"/>
+      <c r="I9" s="55"/>
+      <c r="J9" s="55"/>
+      <c r="K9" s="55"/>
       <c r="L9" s="40" t="s">
         <v>423</v>
       </c>

--- a/GACPAQ pages.xlsx
+++ b/GACPAQ pages.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/doncastillo/Code/gacpaq/gac-paq-app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE4CA96A-15E5-A241-90A2-BD5CC1540E93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C598E79-F3CF-7743-8FFD-6518F40976E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2720" yWindow="780" windowWidth="38400" windowHeight="19140" activeTab="5" xr2:uid="{F0D6E043-EC2B-F746-8C39-25C7730C9E54}"/>
+    <workbookView xWindow="-18660" yWindow="-21000" windowWidth="38400" windowHeight="21000" activeTab="5" xr2:uid="{F0D6E043-EC2B-F746-8C39-25C7730C9E54}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/GACPAQ pages.xlsx
+++ b/GACPAQ pages.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/doncastillo/Code/gacpaq/gac-paq-app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C598E79-F3CF-7743-8FFD-6518F40976E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E57F109-8236-9C44-B350-5D7464212ED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-18660" yWindow="-21000" windowWidth="38400" windowHeight="21000" activeTab="5" xr2:uid="{F0D6E043-EC2B-F746-8C39-25C7730C9E54}"/>
+    <workbookView xWindow="18260" yWindow="-21000" windowWidth="38400" windowHeight="21000" activeTab="5" xr2:uid="{F0D6E043-EC2B-F746-8C39-25C7730C9E54}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="981" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="985" uniqueCount="425">
   <si>
     <t>Page Number</t>
   </si>
@@ -8248,10 +8248,18 @@
       <c r="F9" s="53" t="s">
         <v>337</v>
       </c>
-      <c r="G9" s="55"/>
-      <c r="H9" s="55"/>
-      <c r="I9" s="55"/>
-      <c r="J9" s="55"/>
+      <c r="G9" s="53" t="s">
+        <v>337</v>
+      </c>
+      <c r="H9" s="53" t="s">
+        <v>337</v>
+      </c>
+      <c r="I9" s="53" t="s">
+        <v>337</v>
+      </c>
+      <c r="J9" s="53" t="s">
+        <v>337</v>
+      </c>
       <c r="K9" s="55"/>
       <c r="L9" s="40" t="s">
         <v>423</v>
